--- a/阵营/九素云峰.xlsx
+++ b/阵营/九素云峰.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="3"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="茗伊团队监控数据手册" sheetId="2" r:id="rId1"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2528" uniqueCount="1830">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2536" uniqueCount="1838">
   <si>
     <t>__meta = {</t>
   </si>
@@ -5160,6 +5160,18 @@
     <t>{nClass=20,nIcon=2671,nFrame=7,nTime="5,蓝方·获得古猿·资源+200;90,蓝方·古猿·刷新剩余;95,蓝方·古猿·已经刷新",szName="蓝方·古猿·刷新剩余",nRefresh=0,key="通用·古猿",},</t>
   </si>
   <si>
+    <t>蓝方成功击败了古猿·皓\n</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=2671,nFrame=7,nTime="5,蓝方·获得古猿皓·资源+200;90,蓝方·古猿·刷新剩余;95,蓝方·古猿皓·已经刷新",szName="蓝方·古猿·刷新剩余",nRefresh=2,key="蓝方·古猿·皓",},</t>
+  </si>
+  <si>
+    <t>蓝方成功击败了古猿·洞\n</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=2671,nFrame=7,nTime="5,蓝方·获得古猿洞·资源+200;90,红方·古猿·刷新剩余;95,红方·古猿洞·已经刷新",szName="蓝方·古猿·刷新剩余",nRefresh=2,key="红方·古猿·洞",},</t>
+  </si>
+  <si>
     <t>蓝方成功击败了混沌元晶·皓\n</t>
   </si>
   <si>
@@ -5191,6 +5203,18 @@
   </si>
   <si>
     <t>{nClass=20,nIcon=2671,nFrame=3,nTime="5,红方·获得古猿·资源+200;90,红方·古猿·刷新剩余;95,红方·古猿·已经刷新",szName="红方·古猿·刷新剩余",nRefresh=0,key="通用·古猿",},</t>
+  </si>
+  <si>
+    <t>红方成功击败了古猿·皓\n</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=2671,nFrame=3,nTime="5,红方·获得古猿皓·资源+200;90,蓝方·古猿·刷新剩余;95,蓝方·古猿皓·已经刷新",szName="蓝方·古猿·刷新剩余",nRefresh=2,key="蓝方·古猿·皓",},</t>
+  </si>
+  <si>
+    <t>红方成功击败了古猿·洞\n</t>
+  </si>
+  <si>
+    <t>{nClass=20,nIcon=2671,nFrame=3,nTime="5,红方·获得古猿洞·资源+200;90,红方·古猿·刷新剩余;95,红方·古猿洞·已经刷新",szName="红方·古猿·刷新剩余",nRefresh=2,key="红方·古猿·洞",},</t>
   </si>
   <si>
     <t>红方成功击败了混沌元晶·皓\n</t>
@@ -6764,7 +6788,7 @@
     <row r="4" spans="1:7">
       <c r="A4" s="17" t="str">
         <f ca="1">"nTimeStamp = "&amp;((NOW()-70*365-19)*86400-8*3600)*1000&amp;","</f>
-        <v>nTimeStamp = 1788703819000,</v>
+        <v>nTimeStamp = 1789269526000,</v>
       </c>
       <c r="B4" s="20" t="s">
         <v>11</v>
@@ -8690,7 +8714,7 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
-        <v>1768</v>
+        <v>1776</v>
       </c>
       <c r="E1" t="str">
         <f>A1&amp;B1&amp;C1</f>
@@ -8703,13 +8727,13 @@
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>1769</v>
+        <v>1777</v>
       </c>
       <c r="B2" t="s">
-        <v>1770</v>
+        <v>1778</v>
       </c>
       <c r="C2" t="s">
-        <v>1771</v>
+        <v>1779</v>
       </c>
       <c r="E2" t="str">
         <f>A2&amp;B2&amp;C2</f>
@@ -8718,13 +8742,13 @@
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>1772</v>
+        <v>1780</v>
       </c>
       <c r="B3" t="s">
-        <v>1773</v>
+        <v>1781</v>
       </c>
       <c r="C3" t="s">
-        <v>1774</v>
+        <v>1782</v>
       </c>
       <c r="E3" t="str">
         <f t="shared" ref="E3:E22" si="0">A3&amp;B3&amp;C3</f>
@@ -8733,13 +8757,13 @@
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>1775</v>
+        <v>1783</v>
       </c>
       <c r="B4" t="s">
-        <v>1776</v>
+        <v>1784</v>
       </c>
       <c r="C4" t="s">
-        <v>1777</v>
+        <v>1785</v>
       </c>
       <c r="E4" t="str">
         <f t="shared" si="0"/>
@@ -8748,13 +8772,13 @@
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>1778</v>
+        <v>1786</v>
       </c>
       <c r="B5" t="s">
-        <v>1779</v>
+        <v>1787</v>
       </c>
       <c r="C5" t="s">
-        <v>1780</v>
+        <v>1788</v>
       </c>
       <c r="E5" t="str">
         <f t="shared" si="0"/>
@@ -8763,7 +8787,7 @@
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>1781</v>
+        <v>1789</v>
       </c>
       <c r="E6" t="str">
         <f t="shared" si="0"/>
@@ -8772,13 +8796,13 @@
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>1782</v>
+        <v>1790</v>
       </c>
       <c r="B7" t="s">
-        <v>1783</v>
+        <v>1791</v>
       </c>
       <c r="C7" t="s">
-        <v>1784</v>
+        <v>1792</v>
       </c>
       <c r="E7" t="str">
         <f t="shared" si="0"/>
@@ -8787,13 +8811,13 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>1785</v>
+        <v>1793</v>
       </c>
       <c r="B8" t="s">
-        <v>1786</v>
+        <v>1794</v>
       </c>
       <c r="C8" t="s">
-        <v>1770</v>
+        <v>1778</v>
       </c>
       <c r="E8" t="str">
         <f t="shared" si="0"/>
@@ -8802,13 +8826,13 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>1787</v>
+        <v>1795</v>
       </c>
       <c r="B9" t="s">
-        <v>1788</v>
+        <v>1796</v>
       </c>
       <c r="C9" t="s">
-        <v>1773</v>
+        <v>1781</v>
       </c>
       <c r="E9" t="str">
         <f t="shared" si="0"/>
@@ -8817,13 +8841,13 @@
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>1789</v>
+        <v>1797</v>
       </c>
       <c r="B10" t="s">
-        <v>1790</v>
+        <v>1798</v>
       </c>
       <c r="C10" t="s">
-        <v>1776</v>
+        <v>1784</v>
       </c>
       <c r="E10" t="str">
         <f t="shared" si="0"/>
@@ -8832,13 +8856,13 @@
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>1791</v>
+        <v>1799</v>
       </c>
       <c r="B11" t="s">
-        <v>1792</v>
+        <v>1800</v>
       </c>
       <c r="C11" t="s">
-        <v>1779</v>
+        <v>1787</v>
       </c>
       <c r="E11" t="str">
         <f t="shared" si="0"/>
@@ -8847,7 +8871,7 @@
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
-        <v>1793</v>
+        <v>1801</v>
       </c>
       <c r="E12" t="str">
         <f t="shared" si="0"/>
@@ -8856,10 +8880,10 @@
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
-        <v>1794</v>
+        <v>1802</v>
       </c>
       <c r="C13" t="s">
-        <v>1783</v>
+        <v>1791</v>
       </c>
       <c r="E13" t="str">
         <f t="shared" si="0"/>
@@ -8868,10 +8892,10 @@
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="1" t="s">
-        <v>1795</v>
+        <v>1803</v>
       </c>
       <c r="C14" t="s">
-        <v>1786</v>
+        <v>1794</v>
       </c>
       <c r="E14" t="str">
         <f t="shared" si="0"/>
@@ -8880,10 +8904,10 @@
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="1" t="s">
+        <v>1804</v>
+      </c>
+      <c r="C15" t="s">
         <v>1796</v>
-      </c>
-      <c r="C15" t="s">
-        <v>1788</v>
       </c>
       <c r="E15" t="str">
         <f t="shared" si="0"/>
@@ -8892,10 +8916,10 @@
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="1" t="s">
-        <v>1797</v>
+        <v>1805</v>
       </c>
       <c r="C16" t="s">
-        <v>1790</v>
+        <v>1798</v>
       </c>
       <c r="E16" t="str">
         <f t="shared" si="0"/>
@@ -8904,10 +8928,10 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="1" t="s">
-        <v>1798</v>
+        <v>1806</v>
       </c>
       <c r="C17" t="s">
-        <v>1792</v>
+        <v>1800</v>
       </c>
       <c r="E17" t="str">
         <f t="shared" si="0"/>
@@ -8916,7 +8940,7 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="1" t="s">
-        <v>1799</v>
+        <v>1807</v>
       </c>
       <c r="E18" t="str">
         <f t="shared" si="0"/>
@@ -8925,7 +8949,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="1" t="s">
-        <v>1800</v>
+        <v>1808</v>
       </c>
       <c r="E19" t="str">
         <f t="shared" si="0"/>
@@ -8934,7 +8958,7 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="1" t="s">
-        <v>1801</v>
+        <v>1809</v>
       </c>
       <c r="E20" t="str">
         <f t="shared" si="0"/>
@@ -8943,7 +8967,7 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="1" t="s">
-        <v>1802</v>
+        <v>1810</v>
       </c>
       <c r="E21" t="str">
         <f t="shared" si="0"/>
@@ -8952,7 +8976,7 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="1" t="s">
-        <v>1803</v>
+        <v>1811</v>
       </c>
       <c r="E22" t="str">
         <f t="shared" si="0"/>
@@ -8985,7 +9009,7 @@
         <v>60</v>
       </c>
       <c r="C1" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D1">
         <v>10</v>
@@ -9002,7 +9026,7 @@
         <v>4.8</v>
       </c>
       <c r="I1" t="s">
-        <v>1805</v>
+        <v>1813</v>
       </c>
       <c r="J1" t="str">
         <f>H1&amp;","&amp;I1&amp;";"</f>
@@ -9016,7 +9040,7 @@
         <v>3</v>
       </c>
       <c r="M1" t="s">
-        <v>1805</v>
+        <v>1813</v>
       </c>
       <c r="N1" t="str">
         <f>L1&amp;","&amp;M1&amp;";"</f>
@@ -9030,7 +9054,7 @@
         <v>5</v>
       </c>
       <c r="Q1" t="s">
-        <v>1805</v>
+        <v>1813</v>
       </c>
       <c r="R1" t="str">
         <f>P1&amp;","&amp;Q1&amp;";"</f>
@@ -9050,7 +9074,7 @@
         <v>120</v>
       </c>
       <c r="C2" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D2">
         <f>D1+1</f>
@@ -9069,7 +9093,7 @@
         <v>10</v>
       </c>
       <c r="I2" t="s">
-        <v>1806</v>
+        <v>1814</v>
       </c>
       <c r="J2" t="str">
         <f t="shared" ref="J2:J25" si="1">H2&amp;","&amp;I2&amp;";"</f>
@@ -9080,7 +9104,7 @@
         <v>6</v>
       </c>
       <c r="M2" t="s">
-        <v>1806</v>
+        <v>1814</v>
       </c>
       <c r="N2" t="str">
         <f t="shared" ref="N2:N25" si="2">L2&amp;","&amp;M2&amp;";"</f>
@@ -9091,7 +9115,7 @@
         <v>10</v>
       </c>
       <c r="Q2" t="s">
-        <v>1806</v>
+        <v>1814</v>
       </c>
       <c r="R2" t="str">
         <f t="shared" ref="R2:R25" si="3">P2&amp;","&amp;Q2&amp;";"</f>
@@ -9107,7 +9131,7 @@
         <v>180</v>
       </c>
       <c r="C3" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D3">
         <f t="shared" ref="D3:D10" si="5">D2+1</f>
@@ -9122,7 +9146,7 @@
         <v>14.8</v>
       </c>
       <c r="I3" t="s">
-        <v>1807</v>
+        <v>1815</v>
       </c>
       <c r="J3" t="str">
         <f t="shared" si="1"/>
@@ -9133,7 +9157,7 @@
         <v>9</v>
       </c>
       <c r="M3" t="s">
-        <v>1807</v>
+        <v>1815</v>
       </c>
       <c r="N3" t="str">
         <f t="shared" si="2"/>
@@ -9144,7 +9168,7 @@
         <v>15</v>
       </c>
       <c r="Q3" t="s">
-        <v>1807</v>
+        <v>1815</v>
       </c>
       <c r="R3" t="str">
         <f t="shared" si="3"/>
@@ -9160,7 +9184,7 @@
         <v>240</v>
       </c>
       <c r="C4" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D4">
         <f t="shared" si="5"/>
@@ -9175,7 +9199,7 @@
         <v>20.3</v>
       </c>
       <c r="I4" t="s">
-        <v>1808</v>
+        <v>1816</v>
       </c>
       <c r="J4" t="str">
         <f t="shared" si="1"/>
@@ -9186,7 +9210,7 @@
         <v>12</v>
       </c>
       <c r="M4" t="s">
-        <v>1808</v>
+        <v>1816</v>
       </c>
       <c r="N4" t="str">
         <f t="shared" si="2"/>
@@ -9197,7 +9221,7 @@
         <v>20</v>
       </c>
       <c r="Q4" t="s">
-        <v>1808</v>
+        <v>1816</v>
       </c>
       <c r="R4" t="str">
         <f t="shared" si="3"/>
@@ -9213,7 +9237,7 @@
         <v>300</v>
       </c>
       <c r="C5" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D5">
         <f t="shared" si="5"/>
@@ -9228,7 +9252,7 @@
         <v>25.1</v>
       </c>
       <c r="I5" t="s">
-        <v>1809</v>
+        <v>1817</v>
       </c>
       <c r="J5" t="str">
         <f t="shared" si="1"/>
@@ -9239,7 +9263,7 @@
         <v>15</v>
       </c>
       <c r="M5" t="s">
-        <v>1809</v>
+        <v>1817</v>
       </c>
       <c r="N5" t="str">
         <f t="shared" si="2"/>
@@ -9250,7 +9274,7 @@
         <v>25</v>
       </c>
       <c r="Q5" t="s">
-        <v>1809</v>
+        <v>1817</v>
       </c>
       <c r="R5" t="str">
         <f t="shared" si="3"/>
@@ -9266,7 +9290,7 @@
         <v>360</v>
       </c>
       <c r="C6" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D6">
         <f t="shared" si="5"/>
@@ -9281,7 +9305,7 @@
         <v>30.3</v>
       </c>
       <c r="I6" t="s">
-        <v>1810</v>
+        <v>1818</v>
       </c>
       <c r="J6" t="str">
         <f t="shared" si="1"/>
@@ -9292,7 +9316,7 @@
         <v>18</v>
       </c>
       <c r="M6" t="s">
-        <v>1810</v>
+        <v>1818</v>
       </c>
       <c r="N6" t="str">
         <f t="shared" si="2"/>
@@ -9303,7 +9327,7 @@
         <v>30</v>
       </c>
       <c r="Q6" t="s">
-        <v>1810</v>
+        <v>1818</v>
       </c>
       <c r="R6" t="str">
         <f t="shared" si="3"/>
@@ -9319,7 +9343,7 @@
         <v>420</v>
       </c>
       <c r="C7" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D7">
         <f t="shared" si="5"/>
@@ -9334,7 +9358,7 @@
         <v>35.1</v>
       </c>
       <c r="I7" t="s">
-        <v>1811</v>
+        <v>1819</v>
       </c>
       <c r="J7" t="str">
         <f t="shared" si="1"/>
@@ -9345,7 +9369,7 @@
         <v>21</v>
       </c>
       <c r="M7" t="s">
-        <v>1811</v>
+        <v>1819</v>
       </c>
       <c r="N7" t="str">
         <f t="shared" si="2"/>
@@ -9356,7 +9380,7 @@
         <v>35</v>
       </c>
       <c r="Q7" t="s">
-        <v>1811</v>
+        <v>1819</v>
       </c>
       <c r="R7" t="str">
         <f t="shared" si="3"/>
@@ -9372,7 +9396,7 @@
         <v>480</v>
       </c>
       <c r="C8" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D8">
         <f t="shared" si="5"/>
@@ -9387,7 +9411,7 @@
         <v>40.3</v>
       </c>
       <c r="I8" t="s">
-        <v>1812</v>
+        <v>1820</v>
       </c>
       <c r="J8" t="str">
         <f t="shared" si="1"/>
@@ -9398,7 +9422,7 @@
         <v>24</v>
       </c>
       <c r="M8" t="s">
-        <v>1812</v>
+        <v>1820</v>
       </c>
       <c r="N8" t="str">
         <f t="shared" si="2"/>
@@ -9409,7 +9433,7 @@
         <v>40</v>
       </c>
       <c r="Q8" t="s">
-        <v>1812</v>
+        <v>1820</v>
       </c>
       <c r="R8" t="str">
         <f t="shared" si="3"/>
@@ -9425,7 +9449,7 @@
         <v>540</v>
       </c>
       <c r="C9" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D9">
         <f t="shared" si="5"/>
@@ -9440,7 +9464,7 @@
         <v>45.1</v>
       </c>
       <c r="I9" t="s">
-        <v>1813</v>
+        <v>1821</v>
       </c>
       <c r="J9" t="str">
         <f t="shared" si="1"/>
@@ -9451,7 +9475,7 @@
         <v>27</v>
       </c>
       <c r="M9" t="s">
-        <v>1813</v>
+        <v>1821</v>
       </c>
       <c r="N9" t="str">
         <f t="shared" si="2"/>
@@ -9462,7 +9486,7 @@
         <v>45</v>
       </c>
       <c r="Q9" t="s">
-        <v>1813</v>
+        <v>1821</v>
       </c>
       <c r="R9" t="str">
         <f t="shared" si="3"/>
@@ -9478,7 +9502,7 @@
         <v>600</v>
       </c>
       <c r="C10" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D10">
         <f t="shared" si="5"/>
@@ -9493,7 +9517,7 @@
         <v>50.3</v>
       </c>
       <c r="I10" t="s">
-        <v>1814</v>
+        <v>1822</v>
       </c>
       <c r="J10" t="str">
         <f t="shared" si="1"/>
@@ -9504,7 +9528,7 @@
         <v>30</v>
       </c>
       <c r="M10" t="s">
-        <v>1814</v>
+        <v>1822</v>
       </c>
       <c r="N10" t="str">
         <f t="shared" si="2"/>
@@ -9515,7 +9539,7 @@
         <v>50</v>
       </c>
       <c r="Q10" t="s">
-        <v>1814</v>
+        <v>1822</v>
       </c>
       <c r="R10" t="str">
         <f t="shared" si="3"/>
@@ -9531,7 +9555,7 @@
         <v>660</v>
       </c>
       <c r="C11" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D11">
         <f>D10+2</f>
@@ -9546,7 +9570,7 @@
         <v>55.1</v>
       </c>
       <c r="I11" t="s">
-        <v>1815</v>
+        <v>1823</v>
       </c>
       <c r="J11" t="str">
         <f t="shared" si="1"/>
@@ -9557,7 +9581,7 @@
         <v>33</v>
       </c>
       <c r="M11" t="s">
-        <v>1815</v>
+        <v>1823</v>
       </c>
       <c r="N11" t="str">
         <f t="shared" si="2"/>
@@ -9568,7 +9592,7 @@
         <v>55</v>
       </c>
       <c r="Q11" t="s">
-        <v>1815</v>
+        <v>1823</v>
       </c>
       <c r="R11" t="str">
         <f t="shared" si="3"/>
@@ -9584,7 +9608,7 @@
         <v>720</v>
       </c>
       <c r="C12" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D12">
         <f t="shared" ref="D12:D20" si="8">D11+2</f>
@@ -9599,7 +9623,7 @@
         <v>60.3</v>
       </c>
       <c r="I12" t="s">
-        <v>1816</v>
+        <v>1824</v>
       </c>
       <c r="J12" t="str">
         <f t="shared" si="1"/>
@@ -9610,7 +9634,7 @@
         <v>36</v>
       </c>
       <c r="M12" t="s">
-        <v>1816</v>
+        <v>1824</v>
       </c>
       <c r="N12" t="str">
         <f t="shared" si="2"/>
@@ -9621,7 +9645,7 @@
         <v>60</v>
       </c>
       <c r="Q12" t="s">
-        <v>1816</v>
+        <v>1824</v>
       </c>
       <c r="R12" t="str">
         <f t="shared" si="3"/>
@@ -9637,7 +9661,7 @@
         <v>780</v>
       </c>
       <c r="C13" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D13">
         <f t="shared" si="8"/>
@@ -9652,7 +9676,7 @@
         <v>65.1</v>
       </c>
       <c r="I13" t="s">
-        <v>1817</v>
+        <v>1825</v>
       </c>
       <c r="J13" t="str">
         <f t="shared" si="1"/>
@@ -9663,7 +9687,7 @@
         <v>39</v>
       </c>
       <c r="M13" t="s">
-        <v>1817</v>
+        <v>1825</v>
       </c>
       <c r="N13" t="str">
         <f t="shared" si="2"/>
@@ -9674,7 +9698,7 @@
         <v>65</v>
       </c>
       <c r="Q13" t="s">
-        <v>1817</v>
+        <v>1825</v>
       </c>
       <c r="R13" t="str">
         <f t="shared" si="3"/>
@@ -9690,7 +9714,7 @@
         <v>840</v>
       </c>
       <c r="C14" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D14">
         <f t="shared" si="8"/>
@@ -9705,7 +9729,7 @@
         <v>70.3</v>
       </c>
       <c r="I14" t="s">
-        <v>1818</v>
+        <v>1826</v>
       </c>
       <c r="J14" t="str">
         <f t="shared" si="1"/>
@@ -9716,7 +9740,7 @@
         <v>42</v>
       </c>
       <c r="M14" t="s">
-        <v>1818</v>
+        <v>1826</v>
       </c>
       <c r="N14" t="str">
         <f t="shared" si="2"/>
@@ -9727,7 +9751,7 @@
         <v>70</v>
       </c>
       <c r="Q14" t="s">
-        <v>1818</v>
+        <v>1826</v>
       </c>
       <c r="R14" t="str">
         <f t="shared" si="3"/>
@@ -9743,7 +9767,7 @@
         <v>900</v>
       </c>
       <c r="C15" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D15">
         <f t="shared" si="8"/>
@@ -9758,7 +9782,7 @@
         <v>75.1</v>
       </c>
       <c r="I15" t="s">
-        <v>1819</v>
+        <v>1827</v>
       </c>
       <c r="J15" t="str">
         <f t="shared" si="1"/>
@@ -9769,7 +9793,7 @@
         <v>45</v>
       </c>
       <c r="M15" t="s">
-        <v>1819</v>
+        <v>1827</v>
       </c>
       <c r="N15" t="str">
         <f t="shared" si="2"/>
@@ -9780,7 +9804,7 @@
         <v>75</v>
       </c>
       <c r="Q15" t="s">
-        <v>1819</v>
+        <v>1827</v>
       </c>
       <c r="R15" t="str">
         <f t="shared" si="3"/>
@@ -9796,7 +9820,7 @@
         <v>960</v>
       </c>
       <c r="C16" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D16">
         <f t="shared" si="8"/>
@@ -9811,7 +9835,7 @@
         <v>80.3</v>
       </c>
       <c r="I16" t="s">
-        <v>1820</v>
+        <v>1828</v>
       </c>
       <c r="J16" t="str">
         <f t="shared" si="1"/>
@@ -9822,7 +9846,7 @@
         <v>48</v>
       </c>
       <c r="M16" t="s">
-        <v>1820</v>
+        <v>1828</v>
       </c>
       <c r="N16" t="str">
         <f t="shared" si="2"/>
@@ -9833,7 +9857,7 @@
         <v>80</v>
       </c>
       <c r="Q16" t="s">
-        <v>1820</v>
+        <v>1828</v>
       </c>
       <c r="R16" t="str">
         <f t="shared" si="3"/>
@@ -9849,7 +9873,7 @@
         <v>1020</v>
       </c>
       <c r="C17" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D17">
         <f t="shared" si="8"/>
@@ -9864,7 +9888,7 @@
         <v>85.1</v>
       </c>
       <c r="I17" t="s">
-        <v>1821</v>
+        <v>1829</v>
       </c>
       <c r="J17" t="str">
         <f t="shared" si="1"/>
@@ -9875,7 +9899,7 @@
         <v>51</v>
       </c>
       <c r="M17" t="s">
-        <v>1821</v>
+        <v>1829</v>
       </c>
       <c r="N17" t="str">
         <f t="shared" si="2"/>
@@ -9886,7 +9910,7 @@
         <v>85</v>
       </c>
       <c r="Q17" t="s">
-        <v>1821</v>
+        <v>1829</v>
       </c>
       <c r="R17" t="str">
         <f t="shared" si="3"/>
@@ -9902,7 +9926,7 @@
         <v>1080</v>
       </c>
       <c r="C18" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D18">
         <f t="shared" si="8"/>
@@ -9917,7 +9941,7 @@
         <v>90.3</v>
       </c>
       <c r="I18" t="s">
-        <v>1822</v>
+        <v>1830</v>
       </c>
       <c r="J18" t="str">
         <f t="shared" si="1"/>
@@ -9928,7 +9952,7 @@
         <v>54</v>
       </c>
       <c r="M18" t="s">
-        <v>1822</v>
+        <v>1830</v>
       </c>
       <c r="N18" t="str">
         <f t="shared" si="2"/>
@@ -9939,7 +9963,7 @@
         <v>90</v>
       </c>
       <c r="Q18" t="s">
-        <v>1822</v>
+        <v>1830</v>
       </c>
       <c r="R18" t="str">
         <f t="shared" si="3"/>
@@ -9955,7 +9979,7 @@
         <v>1140</v>
       </c>
       <c r="C19" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D19">
         <f t="shared" si="8"/>
@@ -9970,7 +9994,7 @@
         <v>95.1</v>
       </c>
       <c r="I19" t="s">
-        <v>1823</v>
+        <v>1831</v>
       </c>
       <c r="J19" t="str">
         <f t="shared" si="1"/>
@@ -9981,7 +10005,7 @@
         <v>57</v>
       </c>
       <c r="M19" t="s">
-        <v>1823</v>
+        <v>1831</v>
       </c>
       <c r="N19" t="str">
         <f t="shared" si="2"/>
@@ -9992,7 +10016,7 @@
         <v>95</v>
       </c>
       <c r="Q19" t="s">
-        <v>1823</v>
+        <v>1831</v>
       </c>
       <c r="R19" t="str">
         <f t="shared" si="3"/>
@@ -10008,7 +10032,7 @@
         <v>1200</v>
       </c>
       <c r="C20" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D20">
         <f t="shared" si="8"/>
@@ -10023,7 +10047,7 @@
         <v>100.3</v>
       </c>
       <c r="I20" t="s">
-        <v>1824</v>
+        <v>1832</v>
       </c>
       <c r="J20" t="str">
         <f t="shared" si="1"/>
@@ -10034,7 +10058,7 @@
         <v>60</v>
       </c>
       <c r="M20" t="s">
-        <v>1824</v>
+        <v>1832</v>
       </c>
       <c r="N20" t="str">
         <f t="shared" si="2"/>
@@ -10045,7 +10069,7 @@
         <v>100</v>
       </c>
       <c r="Q20" t="s">
-        <v>1824</v>
+        <v>1832</v>
       </c>
       <c r="R20" t="str">
         <f t="shared" si="3"/>
@@ -10061,7 +10085,7 @@
         <v>1260</v>
       </c>
       <c r="C21" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D21">
         <f>D20+1</f>
@@ -10076,7 +10100,7 @@
         <v>105.1</v>
       </c>
       <c r="I21" t="s">
-        <v>1825</v>
+        <v>1833</v>
       </c>
       <c r="J21" t="str">
         <f t="shared" si="1"/>
@@ -10087,7 +10111,7 @@
         <v>63</v>
       </c>
       <c r="M21" t="s">
-        <v>1825</v>
+        <v>1833</v>
       </c>
       <c r="N21" t="str">
         <f t="shared" si="2"/>
@@ -10098,7 +10122,7 @@
         <v>105</v>
       </c>
       <c r="Q21" t="s">
-        <v>1825</v>
+        <v>1833</v>
       </c>
       <c r="R21" t="str">
         <f t="shared" si="3"/>
@@ -10114,7 +10138,7 @@
         <v>1320</v>
       </c>
       <c r="C22" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D22">
         <f t="shared" ref="D22:D30" si="9">D21+1</f>
@@ -10129,7 +10153,7 @@
         <v>110.3</v>
       </c>
       <c r="I22" t="s">
-        <v>1826</v>
+        <v>1834</v>
       </c>
       <c r="J22" t="str">
         <f t="shared" si="1"/>
@@ -10140,7 +10164,7 @@
         <v>66</v>
       </c>
       <c r="M22" t="s">
-        <v>1826</v>
+        <v>1834</v>
       </c>
       <c r="N22" t="str">
         <f t="shared" si="2"/>
@@ -10151,7 +10175,7 @@
         <v>110</v>
       </c>
       <c r="Q22" t="s">
-        <v>1826</v>
+        <v>1834</v>
       </c>
       <c r="R22" t="str">
         <f t="shared" si="3"/>
@@ -10167,7 +10191,7 @@
         <v>1380</v>
       </c>
       <c r="C23" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D23">
         <f t="shared" si="9"/>
@@ -10182,7 +10206,7 @@
         <v>115.1</v>
       </c>
       <c r="I23" t="s">
-        <v>1827</v>
+        <v>1835</v>
       </c>
       <c r="J23" t="str">
         <f t="shared" si="1"/>
@@ -10193,7 +10217,7 @@
         <v>69</v>
       </c>
       <c r="M23" t="s">
-        <v>1827</v>
+        <v>1835</v>
       </c>
       <c r="N23" t="str">
         <f t="shared" si="2"/>
@@ -10204,7 +10228,7 @@
         <v>115</v>
       </c>
       <c r="Q23" t="s">
-        <v>1827</v>
+        <v>1835</v>
       </c>
       <c r="R23" t="str">
         <f t="shared" si="3"/>
@@ -10220,7 +10244,7 @@
         <v>1440</v>
       </c>
       <c r="C24" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D24">
         <f t="shared" si="9"/>
@@ -10235,7 +10259,7 @@
         <v>120.3</v>
       </c>
       <c r="I24" t="s">
-        <v>1828</v>
+        <v>1836</v>
       </c>
       <c r="J24" t="str">
         <f t="shared" si="1"/>
@@ -10246,7 +10270,7 @@
         <v>72</v>
       </c>
       <c r="M24" t="s">
-        <v>1828</v>
+        <v>1836</v>
       </c>
       <c r="N24" t="str">
         <f t="shared" si="2"/>
@@ -10257,7 +10281,7 @@
         <v>120</v>
       </c>
       <c r="Q24" t="s">
-        <v>1828</v>
+        <v>1836</v>
       </c>
       <c r="R24" t="str">
         <f t="shared" si="3"/>
@@ -10273,7 +10297,7 @@
         <v>1500</v>
       </c>
       <c r="C25" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D25">
         <f t="shared" si="9"/>
@@ -10287,7 +10311,7 @@
         <v>180</v>
       </c>
       <c r="I25" t="s">
-        <v>1829</v>
+        <v>1837</v>
       </c>
       <c r="J25" t="str">
         <f t="shared" si="1"/>
@@ -10297,7 +10321,7 @@
         <v>180</v>
       </c>
       <c r="M25" t="s">
-        <v>1829</v>
+        <v>1837</v>
       </c>
       <c r="N25" t="str">
         <f t="shared" si="2"/>
@@ -10307,7 +10331,7 @@
         <v>180</v>
       </c>
       <c r="Q25" t="s">
-        <v>1829</v>
+        <v>1837</v>
       </c>
       <c r="R25" t="str">
         <f t="shared" si="3"/>
@@ -10323,7 +10347,7 @@
         <v>1560</v>
       </c>
       <c r="C26" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D26">
         <f t="shared" si="9"/>
@@ -10343,7 +10367,7 @@
         <v>1620</v>
       </c>
       <c r="C27" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D27">
         <f t="shared" si="9"/>
@@ -10363,7 +10387,7 @@
         <v>1680</v>
       </c>
       <c r="C28" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D28">
         <f t="shared" si="9"/>
@@ -10383,7 +10407,7 @@
         <v>1740</v>
       </c>
       <c r="C29" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D29">
         <f t="shared" si="9"/>
@@ -10403,7 +10427,7 @@
         <v>1800</v>
       </c>
       <c r="C30" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D30">
         <f t="shared" si="9"/>
@@ -10423,7 +10447,7 @@
         <v>1860</v>
       </c>
       <c r="C31" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D31">
         <f>D30+2</f>
@@ -10443,7 +10467,7 @@
         <v>1920</v>
       </c>
       <c r="C32" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D32">
         <f t="shared" ref="D32:D40" si="10">D31+2</f>
@@ -10463,7 +10487,7 @@
         <v>1980</v>
       </c>
       <c r="C33" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D33">
         <f t="shared" si="10"/>
@@ -10483,7 +10507,7 @@
         <v>2040</v>
       </c>
       <c r="C34" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D34">
         <f t="shared" si="10"/>
@@ -10503,7 +10527,7 @@
         <v>2100</v>
       </c>
       <c r="C35" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D35">
         <f t="shared" si="10"/>
@@ -10523,7 +10547,7 @@
         <v>2160</v>
       </c>
       <c r="C36" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D36">
         <f t="shared" si="10"/>
@@ -10543,7 +10567,7 @@
         <v>2220</v>
       </c>
       <c r="C37" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D37">
         <f t="shared" si="10"/>
@@ -10563,7 +10587,7 @@
         <v>2280</v>
       </c>
       <c r="C38" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D38">
         <f t="shared" si="10"/>
@@ -10583,7 +10607,7 @@
         <v>2340</v>
       </c>
       <c r="C39" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D39">
         <f t="shared" si="10"/>
@@ -10603,7 +10627,7 @@
         <v>2400</v>
       </c>
       <c r="C40" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D40">
         <f t="shared" si="10"/>
@@ -10623,7 +10647,7 @@
         <v>2460</v>
       </c>
       <c r="C41" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D41">
         <f>D40+1</f>
@@ -10643,7 +10667,7 @@
         <v>2520</v>
       </c>
       <c r="C42" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D42">
         <f t="shared" ref="D42:D50" si="11">D41+1</f>
@@ -10663,7 +10687,7 @@
         <v>2580</v>
       </c>
       <c r="C43" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D43">
         <f t="shared" si="11"/>
@@ -10683,7 +10707,7 @@
         <v>2640</v>
       </c>
       <c r="C44" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D44">
         <f t="shared" si="11"/>
@@ -10703,7 +10727,7 @@
         <v>2700</v>
       </c>
       <c r="C45" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D45">
         <f t="shared" si="11"/>
@@ -10723,7 +10747,7 @@
         <v>2760</v>
       </c>
       <c r="C46" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D46">
         <f t="shared" si="11"/>
@@ -10743,7 +10767,7 @@
         <v>2820</v>
       </c>
       <c r="C47" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D47">
         <f t="shared" si="11"/>
@@ -10763,7 +10787,7 @@
         <v>2880</v>
       </c>
       <c r="C48" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D48">
         <f t="shared" si="11"/>
@@ -10783,7 +10807,7 @@
         <v>2940</v>
       </c>
       <c r="C49" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D49">
         <f t="shared" si="11"/>
@@ -10803,7 +10827,7 @@
         <v>3000</v>
       </c>
       <c r="C50" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D50">
         <f t="shared" si="11"/>
@@ -10823,7 +10847,7 @@
         <v>3060</v>
       </c>
       <c r="C51" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D51">
         <f>D50+2</f>
@@ -10843,7 +10867,7 @@
         <v>3120</v>
       </c>
       <c r="C52" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D52">
         <f t="shared" ref="D52:D60" si="13">D51+2</f>
@@ -10863,7 +10887,7 @@
         <v>3180</v>
       </c>
       <c r="C53" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D53">
         <f t="shared" si="13"/>
@@ -10883,7 +10907,7 @@
         <v>3240</v>
       </c>
       <c r="C54" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D54">
         <f t="shared" si="13"/>
@@ -10903,7 +10927,7 @@
         <v>3300</v>
       </c>
       <c r="C55" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D55">
         <f t="shared" si="13"/>
@@ -10923,7 +10947,7 @@
         <v>3360</v>
       </c>
       <c r="C56" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D56">
         <f t="shared" si="13"/>
@@ -10943,7 +10967,7 @@
         <v>3420</v>
       </c>
       <c r="C57" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D57">
         <f t="shared" si="13"/>
@@ -10963,7 +10987,7 @@
         <v>3480</v>
       </c>
       <c r="C58" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D58">
         <f t="shared" si="13"/>
@@ -10983,7 +11007,7 @@
         <v>3540</v>
       </c>
       <c r="C59" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D59">
         <f t="shared" si="13"/>
@@ -11003,7 +11027,7 @@
         <v>3600</v>
       </c>
       <c r="C60" t="s">
-        <v>1804</v>
+        <v>1812</v>
       </c>
       <c r="D60">
         <f t="shared" si="13"/>
@@ -21225,7 +21249,7 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R35"/>
+  <dimension ref="A1:R39"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="3" max="3" width="27.125" customWidth="1"/>
@@ -21295,32 +21319,32 @@
         <v>1701</v>
       </c>
       <c r="N3" t="str">
-        <f t="shared" ref="N3:N35" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(C3),ISBLANK(F3),ISBLANK(G3),OR(ISBLANK(B2)=FALSE,ISBLANK(C2)=FALSE,ISBLANK(F2)=FALSE,ISBLANK(G2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{szContent="""&amp;C3&amp;""","&amp;IF(D3&lt;&gt;"","szNote="""&amp;D3&amp;""",","")&amp;IF(E3&lt;&gt;"","col={"&amp;E3&amp;"},","")&amp;IF(F3&gt;0,"bSearch=true,","")&amp;IF(G3&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(H3&gt;0,"szVoice="""&amp;H3&amp;""",","")&amp;IF(I3&gt;0,"bTeamChannel=true,","")&amp;IF(J3&gt;0,"bWhisperChannel=true,","")&amp;IF(K3&gt;0,"bCenterAlarm=true,","")&amp;IF(L3&gt;0,"bScreenHead=true,","")&amp;IF(M3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(O3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,O3:AAA3)&amp;"},","")&amp;"},")))</f>
+        <f t="shared" ref="N3:N39" si="0">IF(ISBLANK(B3)=FALSE,IF(ISBLANK(B2),"},["&amp;B3&amp;"]={","["&amp;B3&amp;"]={"),IF(AND(ISBLANK(B3),ISBLANK(C3),ISBLANK(F3),ISBLANK(G3),OR(ISBLANK(B2)=FALSE,ISBLANK(C2)=FALSE,ISBLANK(F2)=FALSE,ISBLANK(G2)=FALSE)),"},},}",IF(ISBLANK(C3),"","{szContent="""&amp;C3&amp;""","&amp;IF(D3&lt;&gt;"","szNote="""&amp;D3&amp;""",","")&amp;IF(E3&lt;&gt;"","col={"&amp;E3&amp;"},","")&amp;IF(F3&gt;0,"bSearch=true,","")&amp;IF(G3&gt;0,"bReg=true,","")&amp;"[20]={"&amp;IF(H3&gt;0,"szVoice="""&amp;H3&amp;""",","")&amp;IF(I3&gt;0,"bTeamChannel=true,","")&amp;IF(J3&gt;0,"bWhisperChannel=true,","")&amp;IF(K3&gt;0,"bCenterAlarm=true,","")&amp;IF(L3&gt;0,"bScreenHead=true,","")&amp;IF(M3&gt;0,"bFullScreen=true,","")&amp;"},"&amp;IF(O3&lt;&gt;"","tCountdown={"&amp;_xlfn.TEXTJOIN("",TRUE,O3:AAA3)&amp;"},","")&amp;"},")))</f>
         <v>{szContent="蓝方成功击败了古猿\n",[20]={},tCountdown={{nClass=20,nIcon=2671,nFrame=7,nTime="5,蓝方·获得古猿·资源+200;90,蓝方·古猿·刷新剩余;95,蓝方·古猿·已经刷新",szName="蓝方·古猿·刷新剩余",nRefresh=0,key="通用·古猿",},},},</v>
       </c>
       <c r="O3" t="s">
         <v>1702</v>
       </c>
     </row>
-    <row r="4" spans="1:15">
+    <row r="4" customFormat="1" spans="1:15">
       <c r="C4" t="s">
         <v>1703</v>
       </c>
       <c r="N4" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="蓝方成功击败了混沌元晶·皓\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=7,nTime="5,蓝方·获得元晶皓·资源+100;60,蓝方·元晶·刷新剩余;65,蓝方·元晶·已经刷新",szName="蓝方·元晶·刷新剩余",nRefresh=2,key="蓝方·混沌元晶·皓",},},},</v>
+        <v>{szContent="蓝方成功击败了古猿·皓\n",[20]={},tCountdown={{nClass=20,nIcon=2671,nFrame=7,nTime="5,蓝方·获得古猿皓·资源+200;90,蓝方·古猿·刷新剩余;95,蓝方·古猿皓·已经刷新",szName="蓝方·古猿·刷新剩余",nRefresh=2,key="蓝方·古猿·皓",},},},</v>
       </c>
       <c r="O4" t="s">
         <v>1704</v>
       </c>
     </row>
-    <row r="5" spans="1:15">
+    <row r="5" customFormat="1" spans="1:15">
       <c r="C5" t="s">
         <v>1705</v>
       </c>
       <c r="N5" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="蓝方成功击败了混沌元晶·洞\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=7,nTime="5,蓝方·获得元晶洞·资源+100;60,红方·元晶·刷新剩余;65,红方·元晶·已经刷新",szName="红方·元晶·刷新剩余",nRefresh=2,key="红方·混沌元晶·洞",},},},</v>
+        <v>{szContent="蓝方成功击败了古猿·洞\n",[20]={},tCountdown={{nClass=20,nIcon=2671,nFrame=7,nTime="5,蓝方·获得古猿洞·资源+200;90,红方·古猿·刷新剩余;95,红方·古猿洞·已经刷新",szName="蓝方·古猿·刷新剩余",nRefresh=2,key="红方·古猿·洞",},},},</v>
       </c>
       <c r="O5" t="s">
         <v>1706</v>
@@ -21330,39 +21354,39 @@
       <c r="C6" t="s">
         <v>1707</v>
       </c>
-      <c r="D6" t="s">
-        <v>1708</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
       <c r="N6" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="蓝方成功修复大旗10%耐久度\n",szNote="蓝方·修补·大旗",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=3417,nFrame=7,nTime="5,蓝方·修补大旗·气血+10%;30,蓝方·修补大旗·CD;35,蓝方·修补大旗·就绪",szName="蓝方·修复大旗",nRefresh=0,key="蓝方·修复大旗",},},},</v>
+        <v>{szContent="蓝方成功击败了混沌元晶·皓\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=7,nTime="5,蓝方·获得元晶皓·资源+100;60,蓝方·元晶·刷新剩余;65,蓝方·元晶·已经刷新",szName="蓝方·元晶·刷新剩余",nRefresh=2,key="蓝方·混沌元晶·皓",},},},</v>
       </c>
       <c r="O6" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
     </row>
     <row r="7" spans="1:15">
       <c r="C7" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="N7" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="蓝方成功开启全局迷雾视野\n",[20]={},tCountdown={{nClass=20,nIcon=25111,nFrame=7,nTime="30,蓝方·全局视野·剩余时间;180,蓝方·全局视野·CD;185,蓝方·全局视野·就绪",szName="蓝方·全局视野",nRefresh=0,key="蓝方·全局视野",},},},</v>
+        <v>{szContent="蓝方成功击败了混沌元晶·洞\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=7,nTime="5,蓝方·获得元晶洞·资源+100;60,红方·元晶·刷新剩余;65,红方·元晶·已经刷新",szName="红方·元晶·刷新剩余",nRefresh=2,key="红方·混沌元晶·洞",},},},</v>
       </c>
       <c r="O7" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
     </row>
     <row r="8" spans="1:15">
       <c r="C8" t="s">
+        <v>1711</v>
+      </c>
+      <c r="D8" t="s">
         <v>1712</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
       </c>
       <c r="N8" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="红方成功击败了古猿\n",[20]={},tCountdown={{nClass=20,nIcon=2671,nFrame=3,nTime="5,红方·获得古猿·资源+200;90,红方·古猿·刷新剩余;95,红方·古猿·已经刷新",szName="红方·古猿·刷新剩余",nRefresh=0,key="通用·古猿",},},},</v>
+        <v>{szContent="蓝方成功修复大旗10%耐久度\n",szNote="蓝方·修补·大旗",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=3417,nFrame=7,nTime="5,蓝方·修补大旗·气血+10%;30,蓝方·修补大旗·CD;35,蓝方·修补大旗·就绪",szName="蓝方·修复大旗",nRefresh=0,key="蓝方·修复大旗",},},},</v>
       </c>
       <c r="O8" t="s">
         <v>1713</v>
@@ -21374,7 +21398,7 @@
       </c>
       <c r="N9" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="红方成功击败了混沌元晶·皓\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=3,nTime="5,红方·获得元晶皓·资源+100;60,蓝方·元晶·刷新剩余;65,蓝方·元晶·已经刷新",szName="蓝方·元晶·刷新剩余",nRefresh=2,key="蓝方·混沌元晶·皓",},},},</v>
+        <v>{szContent="蓝方成功开启全局迷雾视野\n",[20]={},tCountdown={{nClass=20,nIcon=25111,nFrame=7,nTime="30,蓝方·全局视野·剩余时间;180,蓝方·全局视野·CD;185,蓝方·全局视野·就绪",szName="蓝方·全局视野",nRefresh=0,key="蓝方·全局视野",},},},</v>
       </c>
       <c r="O9" t="s">
         <v>1715</v>
@@ -21386,55 +21410,43 @@
       </c>
       <c r="N10" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="红方成功击败了混沌元晶·洞\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=3,nTime="5,红方·获得元晶洞·资源+100;60,红方·元晶·刷新剩余;65,红方·元晶·已经刷新",szName="红方·元晶·刷新剩余",nRefresh=2,key="红方·混沌元晶·洞",},},},</v>
+        <v>{szContent="红方成功击败了古猿\n",[20]={},tCountdown={{nClass=20,nIcon=2671,nFrame=3,nTime="5,红方·获得古猿·资源+200;90,红方·古猿·刷新剩余;95,红方·古猿·已经刷新",szName="红方·古猿·刷新剩余",nRefresh=0,key="通用·古猿",},},},</v>
       </c>
       <c r="O10" t="s">
         <v>1717</v>
       </c>
     </row>
-    <row r="11" spans="1:15">
+    <row r="11" customFormat="1" spans="1:15">
       <c r="C11" t="s">
         <v>1718</v>
       </c>
-      <c r="D11" t="s">
-        <v>1719</v>
-      </c>
-      <c r="K11">
-        <v>1</v>
-      </c>
       <c r="N11" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="红方成功修复大旗10%耐久度\n",szNote="红方·修补·大旗",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=3416,nFrame=3,nTime="5,红方·修补大旗·气血+10%;30,红方·修补大旗·CD;35,红方·修补大旗·就绪",szName="红方·修复大旗",nRefresh=0,key="红方·修复大旗",},},},</v>
+        <v>{szContent="红方成功击败了古猿·皓\n",[20]={},tCountdown={{nClass=20,nIcon=2671,nFrame=3,nTime="5,红方·获得古猿皓·资源+200;90,蓝方·古猿·刷新剩余;95,蓝方·古猿皓·已经刷新",szName="蓝方·古猿·刷新剩余",nRefresh=2,key="蓝方·古猿·皓",},},},</v>
       </c>
       <c r="O11" t="s">
+        <v>1719</v>
+      </c>
+    </row>
+    <row r="12" customFormat="1" spans="1:15">
+      <c r="C12" t="s">
         <v>1720</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
-      <c r="C12" t="s">
-        <v>1721</v>
       </c>
       <c r="N12" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="红方成功开启全局迷雾视野\n",[20]={},tCountdown={{nClass=20,nIcon=25109,nFrame=3,nTime="30,红方·全局视野·剩余时间;180,红方·全局视野·CD;185,红方·全局视野·就绪",szName="红方·全局视野",nRefresh=0,key="红方·全局视野",},},},</v>
+        <v>{szContent="红方成功击败了古猿·洞\n",[20]={},tCountdown={{nClass=20,nIcon=2671,nFrame=3,nTime="5,红方·获得古猿洞·资源+200;90,红方·古猿·刷新剩余;95,红方·古猿洞·已经刷新",szName="红方·古猿·刷新剩余",nRefresh=2,key="红方·古猿·洞",},},},</v>
       </c>
       <c r="O12" t="s">
-        <v>1722</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="13" spans="1:15">
       <c r="C13" t="s">
-        <v>1682</v>
-      </c>
-      <c r="D13" t="s">
-        <v>1683</v>
-      </c>
-      <c r="K13">
-        <v>1</v>
+        <v>1722</v>
       </c>
       <c r="N13" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="敌方拾取麒麟珠\n",szNote="敌方·获得·麒麟珠",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=0,nTime="5,敌方获得·麒麟珠·资源+500;240,敌方·麒麟佑·增益剩余;250,敌方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},},},</v>
+        <v>{szContent="红方成功击败了混沌元晶·皓\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=3,nTime="5,红方·获得元晶皓·资源+100;60,蓝方·元晶·刷新剩余;65,蓝方·元晶·已经刷新",szName="蓝方·元晶·刷新剩余",nRefresh=2,key="蓝方·混沌元晶·皓",},},},</v>
       </c>
       <c r="O13" t="s">
         <v>1723</v>
@@ -21442,310 +21454,307 @@
     </row>
     <row r="14" spans="1:15">
       <c r="C14" t="s">
-        <v>1685</v>
-      </c>
-      <c r="D14" t="s">
-        <v>1686</v>
-      </c>
-      <c r="K14">
-        <v>1</v>
+        <v>1724</v>
       </c>
       <c r="N14" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="我方拾取麒麟珠\n",szNote="我方·获得·麒麟珠",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=0,nTime="5,我方获得·麒麟珠·资源+500;240,我方·麒麟佑·增益剩余;250,我方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},},},</v>
+        <v>{szContent="红方成功击败了混沌元晶·洞\n",[20]={},tCountdown={{nClass=20,nIcon=2672,nFrame=3,nTime="5,红方·获得元晶洞·资源+100;60,红方·元晶·刷新剩余;65,红方·元晶·已经刷新",szName="红方·元晶·刷新剩余",nRefresh=2,key="红方·混沌元晶·洞",},},},</v>
       </c>
       <c r="O14" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="15" spans="1:15">
       <c r="C15" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="D15" t="s">
-        <v>1689</v>
+        <v>1727</v>
       </c>
       <c r="K15">
         <v>1</v>
       </c>
       <c r="N15" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="蓝方成功击败了九渊麒麟\n",szNote="蓝方·击伤·九渊麒麟",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失;540,九渊麒麟·刷新剩余;545,九渊麒麟·已经刷新",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},},},</v>
+        <v>{szContent="红方成功修复大旗10%耐久度\n",szNote="红方·修补·大旗",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=3416,nFrame=3,nTime="5,红方·修补大旗·气血+10%;30,红方·修补大旗·CD;35,红方·修补大旗·就绪",szName="红方·修复大旗",nRefresh=0,key="红方·修复大旗",},},},</v>
       </c>
       <c r="O15" t="s">
-        <v>1726</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="16" spans="1:15">
       <c r="C16" t="s">
-        <v>1727</v>
-      </c>
-      <c r="D16" t="s">
-        <v>1692</v>
-      </c>
-      <c r="K16">
-        <v>1</v>
+        <v>1729</v>
       </c>
       <c r="N16" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="红方成功击败了九渊麒麟\n",szNote="红方·击伤·九渊麒麟",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失;540,九渊麒麟·刷新剩余;545,九渊麒麟·已经刷新",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},},},</v>
+        <v>{szContent="红方成功开启全局迷雾视野\n",[20]={},tCountdown={{nClass=20,nIcon=25109,nFrame=3,nTime="30,红方·全局视野·剩余时间;180,红方·全局视野·CD;185,红方·全局视野·就绪",szName="红方·全局视野",nRefresh=0,key="红方·全局视野",},},},</v>
       </c>
       <c r="O16" t="s">
-        <v>1726</v>
+        <v>1730</v>
       </c>
     </row>
     <row r="17" spans="1:18">
       <c r="C17" t="s">
-        <v>1728</v>
+        <v>1682</v>
+      </c>
+      <c r="D17" t="s">
+        <v>1683</v>
+      </c>
+      <c r="K17">
+        <v>1</v>
       </c>
       <c r="N17" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="敌方箭塔被摧毁\n",[20]={},tCountdown={{nClass=20,nIcon=3738,nFrame=3,nTime=10,szName="敌方·箭塔·已被摧毁",key="敌方箭塔",},},},</v>
+        <v>{szContent="敌方拾取麒麟珠\n",szNote="敌方·获得·麒麟珠",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=0,nTime="5,敌方获得·麒麟珠·资源+500;240,敌方·麒麟佑·增益剩余;250,敌方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="O17" t="s">
-        <v>1729</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="18" spans="1:18">
       <c r="C18" t="s">
-        <v>1730</v>
+        <v>1685</v>
+      </c>
+      <c r="D18" t="s">
+        <v>1686</v>
+      </c>
+      <c r="K18">
+        <v>1</v>
       </c>
       <c r="N18" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="我方箭塔被摧毁\n",[20]={},tCountdown={{nClass=20,nIcon=3738,nFrame=2,nTime=10,szName="我方·箭塔·已被摧毁",key="我方箭塔",},},},</v>
+        <v>{szContent="我方拾取麒麟珠\n",szNote="我方·获得·麒麟珠",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=0,nTime="5,我方获得·麒麟珠·资源+500;240,我方·麒麟佑·增益剩余;250,我方·麒麟佑·增益消失;360,九渊麒麟·刷新剩余;365,九渊麒麟·已经刷新",szName="九渊麒麟·刷新剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="O18" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
     </row>
     <row r="19" spans="1:18">
       <c r="C19" t="s">
-        <v>1732</v>
-      </c>
-      <c r="G19">
+        <v>1733</v>
+      </c>
+      <c r="D19" t="s">
+        <v>1689</v>
+      </c>
+      <c r="K19">
         <v>1</v>
       </c>
       <c r="N19" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="我方(.-)路(.-)塔箭塔被攻击",bReg=true,[20]={},tCountdown={{nClass=20,nIcon=3736,nFrame=1,nTime=10,szName="我方·{$1}路·{$2}塔·遭到攻击",key="我方·{$1}·{$2}",},},},</v>
+        <v>{szContent="蓝方成功击败了九渊麒麟\n",szNote="蓝方·击伤·九渊麒麟",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失;540,九渊麒麟·刷新剩余;545,九渊麒麟·已经刷新",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="O19" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="20" spans="1:18">
       <c r="C20" t="s">
-        <v>1734</v>
+        <v>1735</v>
+      </c>
+      <c r="D20" t="s">
+        <v>1692</v>
+      </c>
+      <c r="K20">
+        <v>1</v>
       </c>
       <c r="N20" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="我方大旗遭到攻击\n",[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=2,nTime=10,szName="我方·大旗·遭到攻击",key="我方大旗",},},},</v>
+        <v>{szContent="红方成功击败了九渊麒麟\n",szNote="红方·击伤·九渊麒麟",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=8,nTime="180,麒麟珠·拾取剩余;185,麒麟珠·已经消失;540,九渊麒麟·刷新剩余;545,九渊麒麟·已经刷新",szName="麒麟珠·拾取剩余",nRefresh=0,key="九渊麒麟",},},},</v>
       </c>
       <c r="O20" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="21" spans="1:18">
       <c r="C21" t="s">
         <v>1736</v>
       </c>
-      <c r="D21" t="s">
-        <v>1737</v>
-      </c>
-      <c r="E21" t="s">
-        <v>582</v>
-      </c>
-      <c r="K21">
-        <v>1</v>
-      </c>
-      <c r="M21">
-        <v>1</v>
-      </c>
       <c r="N21" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="九渊麒麟已重生！\n",szNote="九渊麒麟·已经刷新",col={255,255,255,},[20]={bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=1,nTime=5,szName="九渊麒麟·已经刷新",key="九渊麒麟",},},},</v>
+        <v>{szContent="敌方箭塔被摧毁\n",[20]={},tCountdown={{nClass=20,nIcon=3738,nFrame=3,nTime=10,szName="敌方·箭塔·已被摧毁",key="敌方箭塔",},},},</v>
       </c>
       <c r="O21" t="s">
-        <v>1738</v>
+        <v>1737</v>
       </c>
     </row>
     <row r="22" spans="1:18">
       <c r="C22" t="s">
-        <v>1739</v>
-      </c>
-      <c r="D22" t="s">
-        <v>1740</v>
-      </c>
-      <c r="E22" t="s">
-        <v>582</v>
-      </c>
-      <c r="L22">
-        <v>1</v>
+        <v>1738</v>
       </c>
       <c r="N22" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="小麻雀收取了你九十九银。\n",szNote="麻雀·传送",col={255,255,255,},[20]={bScreenHead=true,},},</v>
+        <v>{szContent="我方箭塔被摧毁\n",[20]={},tCountdown={{nClass=20,nIcon=3738,nFrame=2,nTime=10,szName="我方·箭塔·已被摧毁",key="我方箭塔",},},},</v>
+      </c>
+      <c r="O22" t="s">
+        <v>1739</v>
       </c>
     </row>
     <row r="23" spans="1:18">
       <c r="C23" t="s">
-        <v>1741</v>
+        <v>1740</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
       </c>
       <c r="N23" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="战斗开始。\n",[20]={},tCountdown={{nClass=20,nIcon=2401,nFrame=-1,nTime="1,战斗·开始比赛;5,战斗开始·野区资源·已刷新;63,箭塔·减伤·4层·9层·14层;123,箭塔·减伤·3层·8层·13层;183,箭塔·减伤·2层·7层·12层;243,箭塔·减伤·1层·6层·11层;248,一塔·减伤·已消失;303,箭塔·减伤·0层·5层·10层;363,箭塔·减伤·0层·4层·9层;423,箭塔·减伤·0层·3层·8层;483,箭塔·减伤·0层·2层·7层;543,箭塔·减伤·0层·1层·6层;548,二塔·减伤·已消失;603,三塔·减伤·5层;663,三塔·减伤·4层;723,三塔·减伤·3层;783,三塔·减伤·2层;843,三塔·减伤·1层;848,三塔·减伤·已消失;900,九渊麒麟·刷新剩余;901,九渊麒麟·即将刷新;906,九渊麒麟·已经刷新;1200,麻雀传送·开启剩余;1205,麻雀传送·已经开启;2100,修补大旗·禁止剩余;2105,修补大旗·已经禁止;2400,帮会联赛·结束剩余;2400.7,帮会联赛·正在结算;2402,帮会联赛·比赛结束;2700,帮会联赛·5分钟·加时剩余;3000,帮会联赛·10分钟·加时剩余;3300,帮会联赛·15分钟·加时剩余;3600,帮会联赛·20分钟·加时剩余",szName="战斗开始",nRefresh=0,key="战斗开始",},{nClass=20,nIcon=13451,nFrame=4,nTime="60,复活·时间·10秒;120,复活·时间·11秒;180,复活·时间·12秒;240,复活·时间·13秒;300,复活·时间·14秒;360,复活·时间·15秒;420,复活·时间·16秒;480,复活·时间·17秒;540,复活·时间·18秒;600,复活·时间·19秒;660,复活·时间·21秒;720,复活·时间·23秒;780,复活·时间·25秒;840,复活·时间·27秒;900,复活·时间·29秒;960,复活·时间·31秒;1020,复活·时间·33秒;1080,复活·时间·35秒;1140,复活·时间·37秒;1200,复活·时间·39秒;1260,复活·时间·40秒;1320,复活·时间·41秒;1380,复活·时间·42秒;1440,复活·时间·43秒;1500,复活·时间·44秒;1560,复活·时间·45秒;1620,复活·时间·46秒;1680,复活·时间·47秒;1740,复活·时间·48秒;1800,复活·时间·49秒;1860,复活·时间·51秒;1920,复活·时间·53秒;1980,复活·时间·55秒;2040,复活·时间·57秒;2100,复活·时间·59秒;2160,复活·时间·61秒;2220,复活·时间·63秒;2280,复活·时间·65秒;2340,复活·时间·67秒;2400,复活·时间·69秒;2460,复活·时间·70秒;2520,复活·时间·71秒;2580,复活·时间·72秒;2640,复活·时间·73秒;2700,复活·时间·74秒;2760,复活·时间·75秒;2820,复活·时间·76秒;2880,复活·时间·77秒;2940,复活·时间·78秒;3000,复活·时间·79秒;3060,复活·时间·81秒;3120,复活·时间·83秒;3180,复活·时间·85秒;3240,复活·时间·87秒;3300,复活·时间·89秒;3360,复活·时间·91秒;3420,复活·时间·93秒;3480,复活·时间·95秒;3540,复活·时间·97秒;3600,复活·时间·99秒",szName="复活时间",nRefresh=0,key="复活时间",},},},</v>
+        <v>{szContent="我方(.-)路(.-)塔箭塔被攻击",bReg=true,[20]={},tCountdown={{nClass=20,nIcon=3736,nFrame=1,nTime=10,szName="我方·{$1}路·{$2}塔·遭到攻击",key="我方·{$1}·{$2}",},},},</v>
       </c>
       <c r="O23" t="s">
-        <v>1742</v>
-      </c>
-      <c r="P23" t="s">
-        <v>1743</v>
+        <v>1741</v>
       </c>
     </row>
     <row r="24" spans="1:18">
       <c r="C24" t="s">
-        <v>1744</v>
+        <v>1742</v>
       </c>
       <c r="N24" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="战斗将在120秒后开始。\n",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=120,szName="战斗·开始倒计时",key="战斗开始",},{nClass=20,nIcon=21425,nFrame=2,nTime=120,szName="注意·请指挥开启指挥面板",key="绣球花",},{nClass=20,nIcon=21425,nFrame=2,nTime=120,szName="注意·开启剑心焦点·综合聊天框",key="郁金香",},{nClass=20,nIcon=21425,nFrame=2,nTime=120,szName="注意·主信息板小地图·不可折叠",key="牵牛花",},},},</v>
+        <v>{szContent="我方大旗遭到攻击\n",[20]={},tCountdown={{nClass=20,nIcon=592,nFrame=2,nTime=10,szName="我方·大旗·遭到攻击",key="我方大旗",},},},</v>
       </c>
       <c r="O24" t="s">
-        <v>1745</v>
-      </c>
-      <c r="P24" t="s">
-        <v>1746</v>
-      </c>
-      <c r="Q24" t="s">
-        <v>1747</v>
-      </c>
-      <c r="R24" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="25" spans="1:18">
       <c r="C25" t="s">
-        <v>1749</v>
+        <v>1744</v>
+      </c>
+      <c r="D25" t="s">
+        <v>1745</v>
+      </c>
+      <c r="E25" t="s">
+        <v>582</v>
+      </c>
+      <c r="K25">
+        <v>1</v>
+      </c>
+      <c r="M25">
+        <v>1</v>
       </c>
       <c r="N25" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="战斗将在180秒后开始。\n",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=180,szName="战斗·开始倒计时",key="战斗开始",},{nClass=20,nIcon=21425,nFrame=2,nTime=180,szName="注意·请指挥开启指挥面板",key="绣球花",},{nClass=20,nIcon=21425,nFrame=2,nTime=180,szName="注意·开启剑心焦点·综合聊天框",key="郁金香",},{nClass=20,nIcon=21425,nFrame=2,nTime=180,szName="注意·主信息板小地图·不可折叠",key="牵牛花",},},},</v>
+        <v>{szContent="九渊麒麟已重生！\n",szNote="九渊麒麟·已经刷新",col={255,255,255,},[20]={bCenterAlarm=true,bFullScreen=true,},tCountdown={{nClass=20,nIcon=2673,nFrame=1,nTime=5,szName="九渊麒麟·已经刷新",key="九渊麒麟",},},},</v>
       </c>
       <c r="O25" t="s">
-        <v>1750</v>
-      </c>
-      <c r="P25" t="s">
-        <v>1751</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>1752</v>
-      </c>
-      <c r="R25" t="s">
-        <v>1753</v>
+        <v>1746</v>
       </c>
     </row>
     <row r="26" spans="1:18">
       <c r="C26" t="s">
-        <v>1754</v>
+        <v>1747</v>
+      </c>
+      <c r="D26" t="s">
+        <v>1748</v>
+      </c>
+      <c r="E26" t="s">
+        <v>582</v>
+      </c>
+      <c r="L26">
+        <v>1</v>
       </c>
       <c r="N26" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="战斗将在240秒后开始。\n",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=240,szName="战斗·开始倒计时",key="战斗开始",},{nClass=20,nIcon=21425,nFrame=2,nTime=240,szName="注意·请指挥开启指挥面板",key="绣球花",},{nClass=20,nIcon=21425,nFrame=2,nTime=240,szName="注意·开启剑心焦点·综合聊天框",key="郁金香",},{nClass=20,nIcon=21425,nFrame=2,nTime=240,szName="注意·主信息板小地图·不可折叠",key="牵牛花",},},},</v>
-      </c>
-      <c r="O26" t="s">
-        <v>1755</v>
-      </c>
-      <c r="P26" t="s">
-        <v>1756</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>1757</v>
-      </c>
-      <c r="R26" t="s">
-        <v>1758</v>
-      </c>
-    </row>
-    <row r="27" customFormat="1" spans="1:18">
-      <c r="A27" t="s">
-        <v>1549</v>
-      </c>
-      <c r="B27">
-        <v>-2</v>
+        <v>{szContent="小麻雀收取了你九十九银。\n",szNote="麻雀·传送",col={255,255,255,},[20]={bScreenHead=true,},},</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18">
+      <c r="C27" t="s">
+        <v>1749</v>
       </c>
       <c r="N27" t="str">
         <f t="shared" si="0"/>
-        <v>},[-2]={</v>
-      </c>
-    </row>
-    <row r="28" customFormat="1" spans="1:18">
+        <v>{szContent="战斗开始。\n",[20]={},tCountdown={{nClass=20,nIcon=2401,nFrame=-1,nTime="1,战斗·开始比赛;5,战斗开始·野区资源·已刷新;63,箭塔·减伤·4层·9层·14层;123,箭塔·减伤·3层·8层·13层;183,箭塔·减伤·2层·7层·12层;243,箭塔·减伤·1层·6层·11层;248,一塔·减伤·已消失;303,箭塔·减伤·0层·5层·10层;363,箭塔·减伤·0层·4层·9层;423,箭塔·减伤·0层·3层·8层;483,箭塔·减伤·0层·2层·7层;543,箭塔·减伤·0层·1层·6层;548,二塔·减伤·已消失;603,三塔·减伤·5层;663,三塔·减伤·4层;723,三塔·减伤·3层;783,三塔·减伤·2层;843,三塔·减伤·1层;848,三塔·减伤·已消失;900,九渊麒麟·刷新剩余;901,九渊麒麟·即将刷新;906,九渊麒麟·已经刷新;1200,麻雀传送·开启剩余;1205,麻雀传送·已经开启;2100,修补大旗·禁止剩余;2105,修补大旗·已经禁止;2400,帮会联赛·结束剩余;2400.7,帮会联赛·正在结算;2402,帮会联赛·比赛结束;2700,帮会联赛·5分钟·加时剩余;3000,帮会联赛·10分钟·加时剩余;3300,帮会联赛·15分钟·加时剩余;3600,帮会联赛·20分钟·加时剩余",szName="战斗开始",nRefresh=0,key="战斗开始",},{nClass=20,nIcon=13451,nFrame=4,nTime="60,复活·时间·10秒;120,复活·时间·11秒;180,复活·时间·12秒;240,复活·时间·13秒;300,复活·时间·14秒;360,复活·时间·15秒;420,复活·时间·16秒;480,复活·时间·17秒;540,复活·时间·18秒;600,复活·时间·19秒;660,复活·时间·21秒;720,复活·时间·23秒;780,复活·时间·25秒;840,复活·时间·27秒;900,复活·时间·29秒;960,复活·时间·31秒;1020,复活·时间·33秒;1080,复活·时间·35秒;1140,复活·时间·37秒;1200,复活·时间·39秒;1260,复活·时间·40秒;1320,复活·时间·41秒;1380,复活·时间·42秒;1440,复活·时间·43秒;1500,复活·时间·44秒;1560,复活·时间·45秒;1620,复活·时间·46秒;1680,复活·时间·47秒;1740,复活·时间·48秒;1800,复活·时间·49秒;1860,复活·时间·51秒;1920,复活·时间·53秒;1980,复活·时间·55秒;2040,复活·时间·57秒;2100,复活·时间·59秒;2160,复活·时间·61秒;2220,复活·时间·63秒;2280,复活·时间·65秒;2340,复活·时间·67秒;2400,复活·时间·69秒;2460,复活·时间·70秒;2520,复活·时间·71秒;2580,复活·时间·72秒;2640,复活·时间·73秒;2700,复活·时间·74秒;2760,复活·时间·75秒;2820,复活·时间·76秒;2880,复活·时间·77秒;2940,复活·时间·78秒;3000,复活·时间·79秒;3060,复活·时间·81秒;3120,复活·时间·83秒;3180,复活·时间·85秒;3240,复活·时间·87秒;3300,复活·时间·89秒;3360,复活·时间·91秒;3420,复活·时间·93秒;3480,复活·时间·95秒;3540,复活·时间·97秒;3600,复活·时间·99秒",szName="复活时间",nRefresh=0,key="复活时间",},},},</v>
+      </c>
+      <c r="O27" t="s">
+        <v>1750</v>
+      </c>
+      <c r="P27" t="s">
+        <v>1751</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18">
       <c r="C28" t="s">
-        <v>1759</v>
-      </c>
-      <c r="D28" t="s">
-        <v>1760</v>
-      </c>
-      <c r="K28">
-        <v>1</v>
+        <v>1752</v>
       </c>
       <c r="N28" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="练习赛已经报名过了\n",szNote="武林争霸赛·练习赛·已经报名",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·已经报名",key="武林争霸赛",},},},</v>
+        <v>{szContent="战斗将在120秒后开始。\n",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=120,szName="战斗·开始倒计时",key="战斗开始",},{nClass=20,nIcon=21425,nFrame=2,nTime=120,szName="注意·请指挥开启指挥面板",key="绣球花",},{nClass=20,nIcon=21425,nFrame=2,nTime=120,szName="注意·开启剑心焦点·综合聊天框",key="郁金香",},{nClass=20,nIcon=21425,nFrame=2,nTime=120,szName="注意·主信息板小地图·不可折叠",key="牵牛花",},},},</v>
       </c>
       <c r="O28" t="s">
-        <v>1761</v>
+        <v>1753</v>
+      </c>
+      <c r="P28" t="s">
+        <v>1754</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>1755</v>
+      </c>
+      <c r="R28" t="s">
+        <v>1756</v>
       </c>
     </row>
     <row r="29" spans="1:18">
       <c r="C29" t="s">
-        <v>1762</v>
-      </c>
-      <c r="D29" t="s">
-        <v>1763</v>
-      </c>
-      <c r="K29">
-        <v>1</v>
+        <v>1757</v>
       </c>
       <c r="N29" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="练习赛匹配超时\n",szNote="武林争霸赛·练习赛·匹配超时",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·匹配超时",key="武林争霸赛",},},},</v>
+        <v>{szContent="战斗将在180秒后开始。\n",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=180,szName="战斗·开始倒计时",key="战斗开始",},{nClass=20,nIcon=21425,nFrame=2,nTime=180,szName="注意·请指挥开启指挥面板",key="绣球花",},{nClass=20,nIcon=21425,nFrame=2,nTime=180,szName="注意·开启剑心焦点·综合聊天框",key="郁金香",},{nClass=20,nIcon=21425,nFrame=2,nTime=180,szName="注意·主信息板小地图·不可折叠",key="牵牛花",},},},</v>
       </c>
       <c r="O29" t="s">
-        <v>1764</v>
+        <v>1758</v>
+      </c>
+      <c r="P29" t="s">
+        <v>1759</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>1760</v>
+      </c>
+      <c r="R29" t="s">
+        <v>1761</v>
       </c>
     </row>
     <row r="30" spans="1:18">
       <c r="C30" t="s">
-        <v>1765</v>
-      </c>
-      <c r="D30" t="s">
-        <v>1766</v>
+        <v>1762</v>
       </c>
       <c r="N30" t="str">
         <f t="shared" si="0"/>
-        <v>{szContent="未到报名时间，或请重新打开界面!\n",szNote="武林争霸赛·未到报名时间",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·未到报名时间",key="武林争霸赛",},},},</v>
+        <v>{szContent="战斗将在240秒后开始。\n",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=240,szName="战斗·开始倒计时",key="战斗开始",},{nClass=20,nIcon=21425,nFrame=2,nTime=240,szName="注意·请指挥开启指挥面板",key="绣球花",},{nClass=20,nIcon=21425,nFrame=2,nTime=240,szName="注意·开启剑心焦点·综合聊天框",key="郁金香",},{nClass=20,nIcon=21425,nFrame=2,nTime=240,szName="注意·主信息板小地图·不可折叠",key="牵牛花",},},},</v>
       </c>
       <c r="O30" t="s">
-        <v>1767</v>
-      </c>
-    </row>
-    <row r="31" spans="1:18">
+        <v>1763</v>
+      </c>
+      <c r="P30" t="s">
+        <v>1764</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>1765</v>
+      </c>
+      <c r="R30" t="s">
+        <v>1766</v>
+      </c>
+    </row>
+    <row r="31" customFormat="1" spans="1:18">
       <c r="A31" t="s">
-        <v>1552</v>
+        <v>1549</v>
       </c>
       <c r="B31">
-        <v>-21</v>
+        <v>-2</v>
       </c>
       <c r="N31" t="str">
         <f t="shared" si="0"/>
-        <v>},[-21]={</v>
+        <v>},[-2]={</v>
       </c>
     </row>
     <row r="32" customFormat="1" spans="1:18">
       <c r="C32" t="s">
-        <v>1759</v>
+        <v>1767</v>
       </c>
       <c r="D32" t="s">
-        <v>1760</v>
+        <v>1768</v>
       </c>
       <c r="K32">
         <v>1</v>
@@ -21755,15 +21764,15 @@
         <v>{szContent="练习赛已经报名过了\n",szNote="武林争霸赛·练习赛·已经报名",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·已经报名",key="武林争霸赛",},},},</v>
       </c>
       <c r="O32" t="s">
-        <v>1761</v>
-      </c>
-    </row>
-    <row r="33" customFormat="1" spans="3:15">
+        <v>1769</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15">
       <c r="C33" t="s">
-        <v>1762</v>
+        <v>1770</v>
       </c>
       <c r="D33" t="s">
-        <v>1763</v>
+        <v>1771</v>
       </c>
       <c r="K33">
         <v>1</v>
@@ -21773,26 +21782,89 @@
         <v>{szContent="练习赛匹配超时\n",szNote="武林争霸赛·练习赛·匹配超时",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·匹配超时",key="武林争霸赛",},},},</v>
       </c>
       <c r="O33" t="s">
-        <v>1764</v>
-      </c>
-    </row>
-    <row r="34" customFormat="1" spans="3:15">
+        <v>1772</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15">
       <c r="C34" t="s">
-        <v>1765</v>
+        <v>1773</v>
       </c>
       <c r="D34" t="s">
-        <v>1766</v>
+        <v>1774</v>
       </c>
       <c r="N34" t="str">
         <f t="shared" si="0"/>
         <v>{szContent="未到报名时间，或请重新打开界面!\n",szNote="武林争霸赛·未到报名时间",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·未到报名时间",key="武林争霸赛",},},},</v>
       </c>
       <c r="O34" t="s">
+        <v>1775</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15">
+      <c r="A35" t="s">
+        <v>1552</v>
+      </c>
+      <c r="B35">
+        <v>-21</v>
+      </c>
+      <c r="N35" t="str">
+        <f t="shared" si="0"/>
+        <v>},[-21]={</v>
+      </c>
+    </row>
+    <row r="36" customFormat="1" spans="1:15">
+      <c r="C36" t="s">
         <v>1767</v>
       </c>
-    </row>
-    <row r="35" spans="3:15">
-      <c r="N35" t="str">
+      <c r="D36" t="s">
+        <v>1768</v>
+      </c>
+      <c r="K36">
+        <v>1</v>
+      </c>
+      <c r="N36" t="str">
+        <f t="shared" si="0"/>
+        <v>{szContent="练习赛已经报名过了\n",szNote="武林争霸赛·练习赛·已经报名",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·已经报名",key="武林争霸赛",},},},</v>
+      </c>
+      <c r="O36" t="s">
+        <v>1769</v>
+      </c>
+    </row>
+    <row r="37" customFormat="1" spans="1:15">
+      <c r="C37" t="s">
+        <v>1770</v>
+      </c>
+      <c r="D37" t="s">
+        <v>1771</v>
+      </c>
+      <c r="K37">
+        <v>1</v>
+      </c>
+      <c r="N37" t="str">
+        <f t="shared" si="0"/>
+        <v>{szContent="练习赛匹配超时\n",szNote="武林争霸赛·练习赛·匹配超时",[20]={bCenterAlarm=true,},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·练习赛·匹配超时",key="武林争霸赛",},},},</v>
+      </c>
+      <c r="O37" t="s">
+        <v>1772</v>
+      </c>
+    </row>
+    <row r="38" customFormat="1" spans="1:15">
+      <c r="C38" t="s">
+        <v>1773</v>
+      </c>
+      <c r="D38" t="s">
+        <v>1774</v>
+      </c>
+      <c r="N38" t="str">
+        <f t="shared" si="0"/>
+        <v>{szContent="未到报名时间，或请重新打开界面!\n",szNote="武林争霸赛·未到报名时间",[20]={},tCountdown={{nClass=20,nIcon=13,nFrame=4,nTime=10,szName="武林争霸赛·未到报名时间",key="武林争霸赛",},},},</v>
+      </c>
+      <c r="O38" t="s">
+        <v>1775</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15">
+      <c r="N39" t="str">
         <f t="shared" si="0"/>
         <v>},},}</v>
       </c>

--- a/阵营/九素云峰.xlsx
+++ b/阵营/九素云峰.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255" activeTab="8"/>
+    <workbookView windowWidth="27945" windowHeight="12255" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="茗伊团队监控数据手册" sheetId="2" r:id="rId1"/>
@@ -6788,7 +6788,7 @@
     <row r="4" spans="1:7">
       <c r="A4" s="17" t="str">
         <f ca="1">"nTimeStamp = "&amp;((NOW()-70*365-19)*86400-8*3600)*1000&amp;","</f>
-        <v>nTimeStamp = 1789269526000,</v>
+        <v>nTimeStamp = 1790319749000,</v>
       </c>
       <c r="B4" s="20" t="s">
         <v>11</v>
@@ -19278,7 +19278,7 @@
         <v>1</v>
       </c>
       <c r="F5">
-        <v>4573</v>
+        <v>6497</v>
       </c>
       <c r="G5" t="s">
         <v>1524</v>
@@ -19294,7 +19294,7 @@
       </c>
       <c r="AQ5" t="str">
         <f t="shared" si="0"/>
-        <v>{dwID=29019,nLevel=1,nIcon=4573,szName="弹射",nScrutinyType=1,szNote="家园卫士出门抗摔",[1]={bBuffList=true,},[2]={},},</v>
+        <v>{dwID=29019,nLevel=1,nIcon=6497,szName="弹射",nScrutinyType=1,szNote="家园卫士出门抗摔",[1]={bBuffList=true,},[2]={},},</v>
       </c>
     </row>
     <row r="6" spans="1:44">
